--- a/РАБОЧИЙ СТОЛ/машины ПОКОМ КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины ПОКОМ КИ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EDBD34-4640-4183-B238-566020FDBBD0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BE8CE6-0292-4614-AEF4-7618C9E3B097}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>Бердянск</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>Логистон (ПРС)</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
   </si>
 </sst>
 </file>
@@ -864,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -1006,7 +1009,7 @@
       <c r="O4" s="2"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="8">
-        <f t="shared" ref="Q4:Q19" si="0">B4-E4-H4-K4-N4</f>
+        <f t="shared" ref="Q4:Q20" si="0">B4-E4-H4-K4-N4</f>
         <v>0</v>
       </c>
     </row>
@@ -1060,7 +1063,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
@@ -1084,7 +1087,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="24"/>
@@ -1108,7 +1111,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="24"/>
@@ -1131,24 +1134,24 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="11"/>
+      <c r="A10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="5"/>
       <c r="Q10" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1156,7 +1159,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B11" s="26"/>
       <c r="C11" s="27"/>
@@ -1180,7 +1183,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B12" s="26"/>
       <c r="C12" s="27"/>
@@ -1204,7 +1207,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B13" s="26"/>
       <c r="C13" s="27"/>
@@ -1228,7 +1231,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="26"/>
       <c r="C14" s="27"/>
@@ -1252,17 +1255,17 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="11"/>
       <c r="K15" s="9"/>
       <c r="L15" s="10"/>
       <c r="M15" s="11"/>
@@ -1276,17 +1279,17 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="5"/>
       <c r="K16" s="9"/>
       <c r="L16" s="10"/>
       <c r="M16" s="11"/>
@@ -1294,13 +1297,13 @@
       <c r="O16" s="10"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="8">
-        <f t="shared" ref="Q16:Q18" si="1">B16-E16-H16-K16-N16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="27"/>
@@ -1318,13 +1321,13 @@
       <c r="O17" s="10"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="Q17:Q19" si="1">B17-E17-H17-K17-N17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="27"/>
@@ -1346,14 +1349,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="23"/>
+        <v>26</v>
+      </c>
+      <c r="B19" s="26"/>
       <c r="C19" s="27"/>
       <c r="D19" s="28"/>
-      <c r="E19" s="23"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="27"/>
       <c r="G19" s="28"/>
       <c r="H19" s="9"/>
@@ -1366,82 +1369,106 @@
       <c r="O19" s="10"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="23"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
+    <row r="21" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="13">
-        <f t="shared" ref="B20:M20" si="2">SUM(B3:B19)</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="13">
+      <c r="B21" s="13">
+        <f t="shared" ref="B21:M21" si="2">SUM(B3:B20)</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D21" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E21" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F21" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G21" s="15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H21" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I21" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J21" s="15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K21" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L21" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M21" s="15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N20" s="12">
-        <f t="shared" ref="N20:P20" si="3">SUM(N3:N19)</f>
-        <v>0</v>
-      </c>
-      <c r="O20" s="14">
+      <c r="N21" s="12">
+        <f t="shared" ref="N21:P21" si="3">SUM(N3:N20)</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P20" s="15">
+      <c r="P21" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="16">
-        <f>SUM(Q3:Q19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <f>B20/17500</f>
+      <c r="Q21" s="16">
+        <f>SUM(Q3:Q20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f>B21/17500</f>
         <v>0</v>
       </c>
     </row>
